--- a/SGC-CKN/Excel/b555c6ce-0c4d-4442-94ad-dc1d6909169d_Thanh_Hoá_P7-15_D800_30-03-2026.xlsx
+++ b/SGC-CKN/Excel/b555c6ce-0c4d-4442-94ad-dc1d6909169d_Thanh_Hoá_P7-15_D800_30-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="75">
   <si>
     <t>Dự án</t>
   </si>
@@ -115,6 +115,10 @@
     <t>Cát pha xám ghi, xám nâu TT dẻo</t>
   </si>
   <si>
+    <t xml:space="preserve">01:46
+30/03/2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">02:15
 30/03/2026</t>
   </si>
@@ -125,6 +129,10 @@
     <t>Sét xám trắng, xám xanh dẻo chảy</t>
   </si>
   <si>
+    <t xml:space="preserve">02:16
+30/03/2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">05:45
 30/03/2026</t>
   </si>
@@ -155,7 +163,7 @@
     <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">12:40
+    <t xml:space="preserve">12:00
 30/03/2026</t>
   </si>
   <si>
@@ -165,7 +173,7 @@
     <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">13:07
+    <t xml:space="preserve">13:04
 30/03/2026</t>
   </si>
   <si>
@@ -373,12 +381,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDE68A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -404,11 +417,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFED7AA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -554,53 +562,53 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1221,7 +1229,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-3.72</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-6.5</v>
@@ -1230,10 +1238,10 @@
         <v>1.25</v>
       </c>
       <c r="I11" s="5">
-        <v>2.78</v>
+        <v>6.5</v>
       </c>
       <c r="J11" s="8">
-        <v>2.22</v>
+        <v>5.2</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1250,10 +1258,10 @@
         <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12" s="9">
         <v>-6.5</v>
@@ -1262,208 +1270,208 @@
         <v>-8.5</v>
       </c>
       <c r="H12" s="9">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="I12" s="9">
         <v>2</v>
       </c>
-      <c r="J12" s="8">
-        <v>4</v>
+      <c r="J12" s="12">
+        <v>4.14</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="12" t="s">
+      <c r="A13" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="14" t="s">
+      <c r="C13" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="12">
+      <c r="D13" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="13">
         <v>-8.5</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="13">
         <v>-16.7</v>
       </c>
-      <c r="H13" s="12">
-        <v>3.5</v>
-      </c>
-      <c r="I13" s="12">
+      <c r="H13" s="13">
+        <v>3.48</v>
+      </c>
+      <c r="I13" s="13">
         <v>8.2</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="12">
+        <v>2.35</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="16">
+        <v>-16.7</v>
+      </c>
+      <c r="G14" s="16">
+        <v>-21.1</v>
+      </c>
+      <c r="H14" s="16">
+        <v>1.42</v>
+      </c>
+      <c r="I14" s="16">
+        <v>4.4</v>
+      </c>
+      <c r="J14" s="12">
+        <v>3.11</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="19">
+        <v>-21.1</v>
+      </c>
+      <c r="G15" s="19">
+        <v>-24.9</v>
+      </c>
+      <c r="H15" s="19">
+        <v>1.67</v>
+      </c>
+      <c r="I15" s="19">
+        <v>3.8</v>
+      </c>
+      <c r="J15" s="12">
+        <v>2.28</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="22">
+        <v>-24.9</v>
+      </c>
+      <c r="G16" s="22">
+        <v>-34.9</v>
+      </c>
+      <c r="H16" s="22">
+        <v>3.17</v>
+      </c>
+      <c r="I16" s="22">
+        <v>10</v>
+      </c>
+      <c r="J16" s="12">
+        <v>3.16</v>
+      </c>
+      <c r="K16" s="23" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" s="25">
+        <v>-34.9</v>
+      </c>
+      <c r="G17" s="25">
+        <v>-37.4</v>
+      </c>
+      <c r="H17" s="25">
+        <v>1.07</v>
+      </c>
+      <c r="I17" s="25">
+        <v>2.5</v>
+      </c>
+      <c r="J17" s="12">
         <v>2.34</v>
       </c>
-      <c r="K13" s="13" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="F14" s="15">
-        <v>-16.7</v>
-      </c>
-      <c r="G14" s="15">
-        <v>-21.1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>1.42</v>
-      </c>
-      <c r="I14" s="15">
-        <v>4.4</v>
-      </c>
-      <c r="J14" s="8">
-        <v>3.11</v>
-      </c>
-      <c r="K14" s="16" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="18">
-        <v>-21.1</v>
-      </c>
-      <c r="G15" s="18">
-        <v>-24.9</v>
-      </c>
-      <c r="H15" s="18">
-        <v>1.67</v>
-      </c>
-      <c r="I15" s="18">
-        <v>3.8</v>
-      </c>
-      <c r="J15" s="8">
-        <v>2.28</v>
-      </c>
-      <c r="K15" s="19" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="21">
-        <v>-24.9</v>
-      </c>
-      <c r="G16" s="21">
-        <v>-34.9</v>
-      </c>
-      <c r="H16" s="21">
-        <v>3.83</v>
-      </c>
-      <c r="I16" s="21">
-        <v>10</v>
-      </c>
-      <c r="J16" s="8">
-        <v>2.61</v>
-      </c>
-      <c r="K16" s="22" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="24">
-        <v>-34.9</v>
-      </c>
-      <c r="G17" s="24">
-        <v>-37.4</v>
-      </c>
-      <c r="H17" s="24">
-        <v>0.45</v>
-      </c>
-      <c r="I17" s="24">
-        <v>2.5</v>
-      </c>
-      <c r="J17" s="27">
-        <v>5.56</v>
-      </c>
-      <c r="K17" s="25" t="s">
+      <c r="K17" s="26" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F18" s="28">
         <v>-37.4</v>
@@ -1477,28 +1485,28 @@
       <c r="I18" s="28">
         <v>2.7</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="12">
         <v>1.91</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F19" s="31">
         <v>-40.1</v>
@@ -1512,7 +1520,7 @@
       <c r="I19" s="31">
         <v>2.4</v>
       </c>
-      <c r="J19" s="8">
+      <c r="J19" s="12">
         <v>3</v>
       </c>
       <c r="K19" s="32" t="s">
@@ -1521,19 +1529,19 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F20" s="34">
         <v>-42.5</v>
@@ -1547,16 +1555,16 @@
       <c r="I20" s="34">
         <v>2.6</v>
       </c>
-      <c r="J20" s="8">
+      <c r="J20" s="12">
         <v>3.12</v>
       </c>
       <c r="K20" s="35" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -1662,31 +1670,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1703,7 +1711,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-3.72</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-6.5</v>
@@ -1712,10 +1720,10 @@
         <v>1.25</v>
       </c>
       <c r="H2" s="5">
-        <v>2.78</v>
+        <v>6.5</v>
       </c>
       <c r="I2" s="8">
-        <v>2.22</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1738,158 +1746,158 @@
         <v>-8.5</v>
       </c>
       <c r="G3" s="9">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="H3" s="9">
         <v>2</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="12">
+        <v>4.14</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="13">
+        <v>3</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="13">
+        <v>1</v>
+      </c>
+      <c r="E4" s="13">
+        <v>-8.5</v>
+      </c>
+      <c r="F4" s="13">
+        <v>-16.7</v>
+      </c>
+      <c r="G4" s="13">
+        <v>3.48</v>
+      </c>
+      <c r="H4" s="13">
+        <v>8.2</v>
+      </c>
+      <c r="I4" s="12">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="16">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
-        <v>3</v>
-      </c>
-      <c r="B4" s="12" t="s">
+      <c r="B5" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="12">
+      <c r="C5" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="16">
         <v>1</v>
       </c>
-      <c r="E4" s="12">
-        <v>-8.5</v>
-      </c>
-      <c r="F4" s="12">
+      <c r="E5" s="16">
         <v>-16.7</v>
       </c>
-      <c r="G4" s="12">
-        <v>3.5</v>
-      </c>
-      <c r="H4" s="12">
-        <v>8.2</v>
-      </c>
-      <c r="I4" s="8">
+      <c r="F5" s="16">
+        <v>-21.1</v>
+      </c>
+      <c r="G5" s="16">
+        <v>1.42</v>
+      </c>
+      <c r="H5" s="16">
+        <v>4.4</v>
+      </c>
+      <c r="I5" s="12">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="19">
+        <v>5</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="19">
+        <v>1</v>
+      </c>
+      <c r="E6" s="19">
+        <v>-21.1</v>
+      </c>
+      <c r="F6" s="19">
+        <v>-24.9</v>
+      </c>
+      <c r="G6" s="19">
+        <v>1.67</v>
+      </c>
+      <c r="H6" s="19">
+        <v>3.8</v>
+      </c>
+      <c r="I6" s="12">
+        <v>2.28</v>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="22">
+        <v>6</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="22">
+        <v>1</v>
+      </c>
+      <c r="E7" s="22">
+        <v>-24.9</v>
+      </c>
+      <c r="F7" s="22">
+        <v>-34.9</v>
+      </c>
+      <c r="G7" s="22">
+        <v>3.17</v>
+      </c>
+      <c r="H7" s="22">
+        <v>10</v>
+      </c>
+      <c r="I7" s="12">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="25">
+        <v>7</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="25">
+        <v>1</v>
+      </c>
+      <c r="E8" s="25">
+        <v>-34.9</v>
+      </c>
+      <c r="F8" s="25">
+        <v>-37.4</v>
+      </c>
+      <c r="G8" s="25">
+        <v>1.07</v>
+      </c>
+      <c r="H8" s="25">
+        <v>2.5</v>
+      </c>
+      <c r="I8" s="12">
         <v>2.34</v>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="15">
-        <v>4</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="15">
-        <v>1</v>
-      </c>
-      <c r="E5" s="15">
-        <v>-16.7</v>
-      </c>
-      <c r="F5" s="15">
-        <v>-21.1</v>
-      </c>
-      <c r="G5" s="15">
-        <v>1.42</v>
-      </c>
-      <c r="H5" s="15">
-        <v>4.4</v>
-      </c>
-      <c r="I5" s="8">
-        <v>3.11</v>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="18">
-        <v>5</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="18">
-        <v>1</v>
-      </c>
-      <c r="E6" s="18">
-        <v>-21.1</v>
-      </c>
-      <c r="F6" s="18">
-        <v>-24.9</v>
-      </c>
-      <c r="G6" s="18">
-        <v>1.67</v>
-      </c>
-      <c r="H6" s="18">
-        <v>3.8</v>
-      </c>
-      <c r="I6" s="8">
-        <v>2.28</v>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="21">
-        <v>6</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="21">
-        <v>1</v>
-      </c>
-      <c r="E7" s="21">
-        <v>-24.9</v>
-      </c>
-      <c r="F7" s="21">
-        <v>-34.9</v>
-      </c>
-      <c r="G7" s="21">
-        <v>3.83</v>
-      </c>
-      <c r="H7" s="21">
-        <v>10</v>
-      </c>
-      <c r="I7" s="8">
-        <v>2.61</v>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="24">
-        <v>7</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="24">
-        <v>1</v>
-      </c>
-      <c r="E8" s="24">
-        <v>-34.9</v>
-      </c>
-      <c r="F8" s="24">
-        <v>-37.4</v>
-      </c>
-      <c r="G8" s="24">
-        <v>0.45</v>
-      </c>
-      <c r="H8" s="24">
-        <v>2.5</v>
-      </c>
-      <c r="I8" s="27">
-        <v>5.56</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1900,7 +1908,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1917,7 +1925,7 @@
       <c r="H9" s="28">
         <v>2.7</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="12">
         <v>1.91</v>
       </c>
     </row>
@@ -1929,7 +1937,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1946,7 +1954,7 @@
       <c r="H10" s="31">
         <v>2.4</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="12">
         <v>3</v>
       </c>
     </row>
@@ -1958,7 +1966,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
@@ -1975,13 +1983,13 @@
       <c r="H11" s="34">
         <v>2.6</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="12">
         <v>3.12</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B12" s="39" t="s">
         <v>30</v>
@@ -1993,19 +2001,19 @@
         <v>10</v>
       </c>
       <c r="E12" s="39">
-        <v>-3.72</v>
+        <v>0</v>
       </c>
       <c r="F12" s="39">
         <v>-45.1</v>
       </c>
       <c r="G12" s="39">
-        <v>15.67</v>
+        <v>15.58</v>
       </c>
       <c r="H12" s="39">
-        <v>41.38</v>
+        <v>45.1</v>
       </c>
       <c r="I12" s="39">
-        <v>2.64</v>
+        <v>2.89</v>
       </c>
     </row>
   </sheetData>
